--- a/src/data/publications.xlsx
+++ b/src/data/publications.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Намогильные камни\Публикации\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_projects\tombstones\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3989B0E-60F1-4066-9A20-DCA927E2D535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F099D3ED-48FB-4059-9AFD-BE846CCE9DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>type</t>
   </si>
@@ -82,6 +82,21 @@
   </si>
   <si>
     <t>Мухаметшин Д.Г.</t>
+  </si>
+  <si>
+    <t>Булгарские эпиграфические кн 1.pdf</t>
+  </si>
+  <si>
+    <t>Булгарские эпиграфические кн 2.pdf</t>
+  </si>
+  <si>
+    <t>Гумеров И.Г., Ахунов А.М., Усманов В.М.</t>
+  </si>
+  <si>
+    <t>Татарская эпиграфическая традиция. Булгарские эпиграфические памятники XIII–XIV вв. Кн. 1</t>
+  </si>
+  <si>
+    <t>Татарская эпиграфическая традиция. Булгарские эпиграфические памятники XIII–XIV вв. Кн. 2</t>
   </si>
 </sst>
 </file>
@@ -405,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -500,6 +515,40 @@
         <v>2014</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2021</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/data/publications.xlsx
+++ b/src/data/publications.xlsx
@@ -54,7 +54,7 @@
     <t>Юсупов_Г_В_Введение_в_булгаро_татарскую_эпиграфику.pdf</t>
   </si>
   <si>
-    <t>Хамидуллин_и_др_ИСТОРИОГРАФИЯ_ИЗУЧЕНИЯ_БУЛГАРО_ТАТАРСКИХ␍ЭПИГРАФИЧЕСКИХ.pdf</t>
+    <t>Хамидуллин_и_др_ИСТОРИОГРАФИЯ_ИЗУЧЕНИЯ_БУЛГАРО_ТАТАРСКИХ_ЭПИГРАФИЧЕСКИХ.pdf</t>
   </si>
   <si>
     <t>Мухаметшин_Д_Г_Г_В_ЮСУПОВ_И_ПРОБЛЕМЫ_ТАТАРСКОЙ_ЭПИГРАФИКИ.pdf</t>
